--- a/resources/model/predict/result/s1_predict_training_result.xlsx
+++ b/resources/model/predict/result/s1_predict_training_result.xlsx
@@ -500,7 +500,7 @@
         <v>0.5389283419651719</v>
       </c>
       <c r="I2" t="n">
-        <v>13.18903470039368</v>
+        <v>18.41797542572021</v>
       </c>
     </row>
     <row r="3">
@@ -533,7 +533,7 @@
         <v>0.3436410276078906</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1035541693369548</v>
+        <v>0.1546781063079834</v>
       </c>
     </row>
     <row r="4">
@@ -566,7 +566,7 @@
         <v>0.5454072340500785</v>
       </c>
       <c r="I4" t="n">
-        <v>0.680337111155192</v>
+        <v>0.8163243929545084</v>
       </c>
     </row>
     <row r="5">
@@ -599,7 +599,7 @@
         <v>0.5217095726131596</v>
       </c>
       <c r="I5" t="n">
-        <v>14.65965104103088</v>
+        <v>17.13035480181376</v>
       </c>
     </row>
     <row r="6">
@@ -632,7 +632,7 @@
         <v>0.4742729975137428</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005667527516682942</v>
+        <v>0.01051902770996094</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>0.2735053516261445</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3329994678497314</v>
+        <v>0.3953662713368734</v>
       </c>
     </row>
     <row r="8">
@@ -683,22 +683,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7858949284352295</v>
+        <v>0.7850513469350361</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00334673887173321</v>
+        <v>0.0004213526194742648</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7812629806343282</v>
+        <v>0.7798773669155157</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7858949284352295</v>
+        <v>0.7850513469350361</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7812501031173719</v>
+        <v>0.7799770606251629</v>
       </c>
       <c r="I8" t="n">
-        <v>105.7279690901438</v>
+        <v>110.4228150844574</v>
       </c>
     </row>
     <row r="9">
@@ -716,22 +716,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.2061946359665011</v>
+        <v>0.2122416141170465</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001815515628884696</v>
+        <v>0.001543592193730424</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1924152692971558</v>
+        <v>0.1959117663308404</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2061946359665011</v>
+        <v>0.2122416141170465</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1854565500568352</v>
+        <v>0.18854633994073</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5516765912373861</v>
+        <v>0.6909241676330566</v>
       </c>
     </row>
     <row r="10">
@@ -749,22 +749,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7383630814732852</v>
+        <v>0.7482072423876902</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001094679130118123</v>
+        <v>0.005138825117992577</v>
       </c>
       <c r="F10" t="n">
-        <v>0.736258894140259</v>
+        <v>0.7463235377052283</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7383630814732852</v>
+        <v>0.7482072423876902</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7278311694946287</v>
+        <v>0.7389327430992815</v>
       </c>
       <c r="I10" t="n">
-        <v>3.342836300532023</v>
+        <v>3.76034140586853</v>
       </c>
     </row>
     <row r="11">
@@ -782,22 +782,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6924832209370023</v>
+        <v>0.6914638529678353</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01454395264289435</v>
+        <v>0.003266400007179949</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6677396765785429</v>
+        <v>0.6640057137912123</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6924832209370023</v>
+        <v>0.6914638529678353</v>
       </c>
       <c r="H11" t="n">
-        <v>0.674058311451982</v>
+        <v>0.6708826877518977</v>
       </c>
       <c r="I11" t="n">
-        <v>86.45933103561401</v>
+        <v>118.6351381937663</v>
       </c>
     </row>
     <row r="12">
@@ -815,22 +815,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.2309451883707245</v>
+        <v>0.2354452759988462</v>
       </c>
       <c r="E12" t="n">
-        <v>0.006892175238495037</v>
+        <v>0.004628185182178095</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2320997218706637</v>
+        <v>0.2372081870412045</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2309451883707245</v>
+        <v>0.2354452759988462</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2137422982086071</v>
+        <v>0.2158883905029906</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01433348655700684</v>
+        <v>0.01767412821451823</v>
       </c>
     </row>
     <row r="13">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.09974059139345383</v>
+        <v>0.1144346924216592</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02140842311431045</v>
+        <v>0.01776710694511269</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07347567212445735</v>
+        <v>0.1098670461838579</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09974059139345383</v>
+        <v>0.1144346924216592</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05045441888272831</v>
+        <v>0.08318568610246187</v>
       </c>
       <c r="I13" t="n">
-        <v>0.832856814066569</v>
+        <v>1.215803543726603</v>
       </c>
     </row>
     <row r="14">
@@ -872,7 +872,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tomek-Links</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -896,7 +896,7 @@
         <v>0.5996364890434824</v>
       </c>
       <c r="I14" t="n">
-        <v>11.07624363899231</v>
+        <v>14.28563825289408</v>
       </c>
     </row>
     <row r="15">
@@ -905,7 +905,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tomek-Links</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -929,7 +929,7 @@
         <v>0.355317758143654</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0793622334798177</v>
+        <v>0.09668358167012532</v>
       </c>
     </row>
     <row r="16">
@@ -938,7 +938,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tomek-Links</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -962,7 +962,7 @@
         <v>0.6121510005225755</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6210066477457682</v>
+        <v>0.7332345644632975</v>
       </c>
     </row>
     <row r="17">
@@ -971,7 +971,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tomek-Links</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -995,7 +995,7 @@
         <v>0.6000085298908544</v>
       </c>
       <c r="I17" t="n">
-        <v>16.69381165504456</v>
+        <v>18.90119997660319</v>
       </c>
     </row>
     <row r="18">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tomek-Links</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1028,7 +1028,7 @@
         <v>0.439329776020807</v>
       </c>
       <c r="I18" t="n">
-        <v>0.006997267405192058</v>
+        <v>0.01105801264444987</v>
       </c>
     </row>
     <row r="19">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tomek-Links</t>
+          <t>Tomek</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1061,7 +1061,7 @@
         <v>0.2010180598179411</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3008882204691569</v>
+        <v>0.3002197742462158</v>
       </c>
     </row>
     <row r="20">
@@ -1079,22 +1079,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.7944483622857871</v>
+        <v>0.7950483899403783</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00404730359212687</v>
+        <v>0.005059795936145867</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7900199859303282</v>
+        <v>0.7902234244676793</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7944483622857871</v>
+        <v>0.7950483899403783</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7897202681745675</v>
+        <v>0.7902135033892491</v>
       </c>
       <c r="I20" t="n">
-        <v>96.14668758710225</v>
+        <v>104.9446747303009</v>
       </c>
     </row>
     <row r="21">
@@ -1112,22 +1112,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.2100577244739264</v>
+        <v>0.2124478224575532</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001119734755503808</v>
+        <v>0.001732662935556956</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1940407159661928</v>
+        <v>0.1984320348969727</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2100577244739264</v>
+        <v>0.2124478224575532</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1891892086457855</v>
+        <v>0.1876882693571983</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5283340613047282</v>
+        <v>0.6555666923522949</v>
       </c>
     </row>
     <row r="22">
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.7509372350588546</v>
+        <v>0.7536761295840115</v>
       </c>
       <c r="E22" t="n">
-        <v>0.002092363269792542</v>
+        <v>0.004034004988230555</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7503298898927845</v>
+        <v>0.7525275928759484</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7509372350588546</v>
+        <v>0.7536761295840115</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7415888004067673</v>
+        <v>0.7442940532520993</v>
       </c>
       <c r="I22" t="n">
-        <v>3.49366021156311</v>
+        <v>3.688763697942098</v>
       </c>
     </row>
     <row r="23">
@@ -1178,22 +1178,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.7020908843594448</v>
+        <v>0.7086636724301337</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0008053924079293593</v>
+        <v>0.001572832145206566</v>
       </c>
       <c r="F23" t="n">
-        <v>0.67897292955149</v>
+        <v>0.6892609960358144</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7020908843594448</v>
+        <v>0.7086636724301337</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6818025958442983</v>
+        <v>0.6904619987807377</v>
       </c>
       <c r="I23" t="n">
-        <v>85.80422123273213</v>
+        <v>104.4593562285105</v>
       </c>
     </row>
     <row r="24">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.2347512246382933</v>
+        <v>0.2378907678356267</v>
       </c>
       <c r="E24" t="n">
-        <v>0.003996025648238668</v>
+        <v>0.004969998434726353</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2376499091488091</v>
+        <v>0.2379273360958142</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2347512246382933</v>
+        <v>0.2378907678356267</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2178119267220935</v>
+        <v>0.2176837162133597</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01433372497558594</v>
+        <v>0.01252341270446777</v>
       </c>
     </row>
     <row r="25">
@@ -1244,22 +1244,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.1102737168722615</v>
+        <v>0.1272526681725514</v>
       </c>
       <c r="E25" t="n">
-        <v>0.006482316404136758</v>
+        <v>0.0115840725773305</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1296319705546007</v>
+        <v>0.1143023283557883</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1102737168722615</v>
+        <v>0.1272526681725514</v>
       </c>
       <c r="H25" t="n">
-        <v>0.07223372378216773</v>
+        <v>0.08860634869696997</v>
       </c>
       <c r="I25" t="n">
-        <v>0.9363205432891846</v>
+        <v>0.9821199576059977</v>
       </c>
     </row>
     <row r="26">
@@ -1277,22 +1277,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8009449001539369</v>
+        <v>0.7984773385170064</v>
       </c>
       <c r="E26" t="n">
-        <v>0.00451400391538248</v>
+        <v>0.003110053270581833</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7949493761009189</v>
+        <v>0.7924774202054289</v>
       </c>
       <c r="G26" t="n">
-        <v>0.8009449001539369</v>
+        <v>0.7984773385170064</v>
       </c>
       <c r="H26" t="n">
-        <v>0.795750337314753</v>
+        <v>0.793653428223672</v>
       </c>
       <c r="I26" t="n">
-        <v>92.39632550875346</v>
+        <v>94.81358480453491</v>
       </c>
     </row>
     <row r="27">
@@ -1310,22 +1310,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.2074093079364602</v>
+        <v>0.2095245013481928</v>
       </c>
       <c r="E27" t="n">
-        <v>0.004485528986347923</v>
+        <v>0.002878685816234385</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2134732083990495</v>
+        <v>0.2167214117775154</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2074093079364602</v>
+        <v>0.2095245013481928</v>
       </c>
       <c r="H27" t="n">
-        <v>0.192087762510516</v>
+        <v>0.1938968232436304</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5162955125172933</v>
+        <v>0.6502145926157633</v>
       </c>
     </row>
     <row r="28">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7538509979357988</v>
+        <v>0.7493744356934625</v>
       </c>
       <c r="E28" t="n">
-        <v>0.003912118981861033</v>
+        <v>0.002381819905423613</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7523137518624931</v>
+        <v>0.7491011088681532</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7538509979357988</v>
+        <v>0.7493744356934625</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7426979088264835</v>
+        <v>0.7385800168208819</v>
       </c>
       <c r="I28" t="n">
-        <v>3.210010290145874</v>
+        <v>4.038572311401367</v>
       </c>
     </row>
     <row r="29">
@@ -1376,22 +1376,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.7162044273361046</v>
+        <v>0.718671649770347</v>
       </c>
       <c r="E29" t="n">
-        <v>0.009755703443821881</v>
+        <v>0.005665249576126749</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6942472684520838</v>
+        <v>0.6971293116613305</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7162044273361046</v>
+        <v>0.718671649770347</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6999005376884276</v>
+        <v>0.7031044049913611</v>
       </c>
       <c r="I29" t="n">
-        <v>107.1157585779826</v>
+        <v>105.2815203666687</v>
       </c>
     </row>
     <row r="30">
@@ -1409,22 +1409,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.2239063412026568</v>
+        <v>0.2248229115954001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.004674054405561257</v>
+        <v>0.006144284507186696</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2515198378962947</v>
+        <v>0.2521998705644656</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2239063412026568</v>
+        <v>0.2248229115954001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.216325237226598</v>
+        <v>0.2179397323180644</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0149998664855957</v>
+        <v>0.01705058415730794</v>
       </c>
     </row>
     <row r="31">
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1151963154566509</v>
+        <v>0.1118475499665688</v>
       </c>
       <c r="E31" t="n">
-        <v>0.007737962461926823</v>
+        <v>0.01038662856554798</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1149607312796765</v>
+        <v>0.09633301899331681</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1151963154566509</v>
+        <v>0.1118475499665688</v>
       </c>
       <c r="H31" t="n">
-        <v>0.08320542327348547</v>
+        <v>0.07489360394679991</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9421263535817465</v>
+        <v>1.052104234695435</v>
       </c>
     </row>
   </sheetData>
